--- a/www/download/IND.hours_worked.empe.s.hr.rpA1.xlsx
+++ b/www/download/IND.hours_worked.empe.s.hr.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12828.687</t>
+          <t>12828686900</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12974.476</t>
+          <t>12974476100</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13053.68</t>
+          <t>13053680400</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13459.16</t>
+          <t>13459159500</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>13759.368</t>
+          <t>13759368400</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14064.941</t>
+          <t>14064941400</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14063.118</t>
+          <t>14063117500</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14373.529</t>
+          <t>14373529200</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>14680.712</t>
+          <t>14680711620</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15143.81</t>
+          <t>15143809500</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>15580.662</t>
+          <t>15580661526.7842</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>15917.851</t>
+          <t>15917851279.2693</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>16341.758</t>
+          <t>16341757580.232</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>17671.991</t>
+          <t>17671991252.385</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>18590.196</t>
+          <t>18590195705.1333</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4827.845</t>
+          <t>4827845000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4833.915</t>
+          <t>4833915000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4916.552</t>
+          <t>4916552000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4991.233</t>
+          <t>4991233000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5053.095</t>
+          <t>5053095000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5121.332</t>
+          <t>5121332000</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5161.275</t>
+          <t>5161275000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5133.78</t>
+          <t>5133780000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>5169.977</t>
+          <t>5169977000</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5204.784</t>
+          <t>5204784000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>5217.574</t>
+          <t>5217574000</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5277.349</t>
+          <t>5277349000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>5371.388</t>
+          <t>5371388000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>5486.016</t>
+          <t>5486016000</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>5327.349</t>
+          <t>5327349000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4595.1</t>
+          <t>4595100000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4585.6</t>
+          <t>4585600000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4644.6</t>
+          <t>4644600000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4729.2</t>
+          <t>4729200000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4818.4</t>
+          <t>4818400000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4982.1</t>
+          <t>4982100000</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5057.8</t>
+          <t>5057800000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5033.1</t>
+          <t>5033100000</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5028.4</t>
+          <t>5028400000</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5082.2</t>
+          <t>5082200000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5.144e+09</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5218.2</t>
+          <t>5218200000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>5322.6</t>
+          <t>5322600000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>5400.1</t>
+          <t>5400100000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>5284.4</t>
+          <t>5284400000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4763.822</t>
+          <t>4763821895.65152</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4804.766</t>
+          <t>4804766257.4269</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4583.11</t>
+          <t>4583109986.79267</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4317.376</t>
+          <t>4317376468.78796</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4123.538</t>
+          <t>4123537525.08647</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3934.009</t>
+          <t>3934009000</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3898.358</t>
+          <t>3898358000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3902.291</t>
+          <t>3902291000</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4004.834</t>
+          <t>4004834000</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4138.132</t>
+          <t>4138132000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4244.756</t>
+          <t>4244756000</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4411.226</t>
+          <t>4411226000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4582.662</t>
+          <t>4582661529.17968</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4717.103</t>
+          <t>4717103117.13106</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4560.187</t>
+          <t>4560187201.07867</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>124855.477</t>
+          <t>124855477356.272</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>122981.929</t>
+          <t>122981929130.877</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>125000.246</t>
+          <t>125000245608.597</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>124217.313</t>
+          <t>124217313012.641</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>128568.971</t>
+          <t>128568970516.355</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>133539.152</t>
+          <t>133539151699.074</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>134738.042</t>
+          <t>134738041576.624</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>140161.944</t>
+          <t>140161944231.357</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>142510.189</t>
+          <t>142510188701.274</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>149104.054</t>
+          <t>149104053980.659</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>151507.858</t>
+          <t>151507858121.156</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>154756.786</t>
+          <t>154756786038.698</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>156829.399</t>
+          <t>156829398560.943</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>159080.283</t>
+          <t>159080283416.758</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>159733.056</t>
+          <t>159733056266.715</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21474.27</t>
+          <t>21474270065.9936</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21728.47</t>
+          <t>21728470234.0654</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21998.085</t>
+          <t>21998084998.91</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22407.136</t>
+          <t>22407135998.91</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>23096.434</t>
+          <t>23096433998.91</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>23762.495</t>
+          <t>23762494998.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24065.074</t>
+          <t>24065073998.91</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24452.873</t>
+          <t>24452872998.91</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>24822.944</t>
+          <t>24822943998.91</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25528.033</t>
+          <t>25528032998.91</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>25761.811</t>
+          <t>25761810998.91</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>26246.008</t>
+          <t>26246007998.91</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>26776.738</t>
+          <t>26776737998.91</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>27188.563</t>
+          <t>27188562998.91</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>26224.348</t>
+          <t>26224347998.91</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>412150.393</t>
+          <t>412150392859.309</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>426369.92</t>
+          <t>426369920378.008</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>438823.592</t>
+          <t>438823592454.172</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>447618.682</t>
+          <t>447618682394.545</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>457002.426</t>
+          <t>457002425684.421</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>476387.581</t>
+          <t>476387580510.376</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>516864.339</t>
+          <t>516864338675.477</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>552146.561</t>
+          <t>552146560740.986</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>580054.797</t>
+          <t>580054796877.443</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>604918.813</t>
+          <t>604918813097.261</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>619932.858</t>
+          <t>619932858057.87</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>627893.215</t>
+          <t>627893214636.227</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>652375.947</t>
+          <t>652375946517.384</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>685347.872</t>
+          <t>685347872401.688</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>706605.398</t>
+          <t>706605398114.285</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>385.082</t>
+          <t>385081830.189556</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>388.735</t>
+          <t>388735218.183415</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>393.173</t>
+          <t>393173063.331875</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>400.651</t>
+          <t>400650693.290692</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>410.296</t>
+          <t>410295651.543646</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>421.155</t>
+          <t>421155000</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>433.872</t>
+          <t>433872000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>443.031</t>
+          <t>443031000</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>455.955</t>
+          <t>455955000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>458.638</t>
+          <t>458638000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>473.113</t>
+          <t>473113000</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>494.479</t>
+          <t>494479000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>516.413</t>
+          <t>516413000</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>540.57</t>
+          <t>540570000</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>541.705</t>
+          <t>541705000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8581.482</t>
+          <t>8581482000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8594.152</t>
+          <t>8594152000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8546.09</t>
+          <t>8546090000</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>8336.71</t>
+          <t>8336710000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8137.807</t>
+          <t>8137807000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8094.805</t>
+          <t>8094805000</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7714.352</t>
+          <t>7714352000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>7569.647</t>
+          <t>7569647000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7358.729</t>
+          <t>7358729000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7481.786</t>
+          <t>7481786000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7685.812</t>
+          <t>7685812000</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>7832.395</t>
+          <t>7832395000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>8030.064</t>
+          <t>8030064000</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>8156.526</t>
+          <t>8156526000</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>8002.884</t>
+          <t>8002883825.01644</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>49333.493</t>
+          <t>49333493412.3921</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48495.041</t>
+          <t>48495041184.2737</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>47917.779</t>
+          <t>47917778993.4606</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>48296.046</t>
+          <t>48296045892.6359</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>48623.541</t>
+          <t>48623541304.493</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>48867.203</t>
+          <t>48867203486.7267</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>48588.388</t>
+          <t>48588388114.2661</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>47915</t>
+          <t>4.7915e+10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>47126</t>
+          <t>4.7126e+10</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>4.7259e+10</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>46689</t>
+          <t>4.6689e+10</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>46883</t>
+          <t>4.6883e+10</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>4.7776e+10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>4.841e+10</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>46952.701</t>
+          <t>46952701355.6198</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3561.707</t>
+          <t>3561707000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3580.474</t>
+          <t>3580474000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3694.916</t>
+          <t>3694916000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3793.961</t>
+          <t>3793961000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3866.816</t>
+          <t>3866816000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3914.097</t>
+          <t>3914097000</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3978.711</t>
+          <t>3978711000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3945.645</t>
+          <t>3945645000</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3897.167</t>
+          <t>3897167000</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3895.572</t>
+          <t>3895572000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3953.214</t>
+          <t>3953214000</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4060.536</t>
+          <t>4060536000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>4152.28</t>
+          <t>4152280000</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>4239.784</t>
+          <t>4239783579</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>4075.162</t>
+          <t>4075161790.5794</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18384.955</t>
+          <t>18384954800</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18810.323</t>
+          <t>18810322900</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19852.46</t>
+          <t>19852460200</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20871.514</t>
+          <t>20871513900</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22043.548</t>
+          <t>22043548100</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23299.203</t>
+          <t>23299203000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24047.748</t>
+          <t>24047748300</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24668.354</t>
+          <t>24668354200</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>25346.447</t>
+          <t>25346447300</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>26060.341</t>
+          <t>26060341300</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>26899.087</t>
+          <t>26899086800</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>27871.875</t>
+          <t>27871875300</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>28470.212</t>
+          <t>28470211500</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>28549.186</t>
+          <t>28549185900</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>26760.757</t>
+          <t>26760757000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1102.698</t>
+          <t>1102698335.57299</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1071.376</t>
+          <t>1071375723.00998</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1064.047</t>
+          <t>1064046584.46363</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1038.062</t>
+          <t>1038061970.02459</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>992.222</t>
+          <t>992221810.700474</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>975.926</t>
+          <t>975925914</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>995.82</t>
+          <t>995819565.683451</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1009.111</t>
+          <t>1009110983</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1022.755</t>
+          <t>1022754578</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1018.847</t>
+          <t>1018847478.2451</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1073.443</t>
+          <t>1073443327</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1141.254</t>
+          <t>1141254371</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1140.255</t>
+          <t>1140254722.30617</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1141.369</t>
+          <t>1141368776</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>952.965</t>
+          <t>952964600.63245</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2.929e+09</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2963.1</t>
+          <t>2963100000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3079.1</t>
+          <t>3079100000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3160.6</t>
+          <t>3160600000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3234.5</t>
+          <t>3234500000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3.295e+09</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3338.8</t>
+          <t>3338800000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3372.6</t>
+          <t>3372600000</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3374.3</t>
+          <t>3374300000</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3397.5</t>
+          <t>3397500000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3436.3</t>
+          <t>3436300000</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3485.8</t>
+          <t>3485800000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>3563.4</t>
+          <t>3563400000</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3620.7</t>
+          <t>3620700000</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3434.5</t>
+          <t>3434500000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>31468.573</t>
+          <t>31468572871.479</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31797.298</t>
+          <t>31797297552.2686</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31910.139</t>
+          <t>31910139313.0704</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>32356.773</t>
+          <t>32356772876.0978</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>33060.697</t>
+          <t>33060696770.3918</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>33182.202</t>
+          <t>33182201967.4061</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>33644.776</t>
+          <t>33644775867.4926</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>33067.66</t>
+          <t>33067659896.5064</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>33001.137</t>
+          <t>33001137358.75</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>33623.177</t>
+          <t>33623177266.6708</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>33760.725</t>
+          <t>33760724650.5758</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>33683.49</t>
+          <t>33683489572.0406</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>34563.816</t>
+          <t>34563815576.0508</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>34927.705</t>
+          <t>34927704665.6024</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>34397.205</t>
+          <t>34397205461.9189</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>38627.754</t>
+          <t>38627753854.3556</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>39074.066</t>
+          <t>39074066076.0412</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>39982.918</t>
+          <t>39982918276.1454</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40493.614</t>
+          <t>40493614132.8693</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>40906.739</t>
+          <t>40906739232.4566</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>41325.285</t>
+          <t>41325285081.1633</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>41761.52</t>
+          <t>41761519662.1478</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>41540.623</t>
+          <t>41540623204.3714</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>41156.943</t>
+          <t>41156942501.4695</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>41469.329</t>
+          <t>41469328891.795</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>42032.235</t>
+          <t>42032235228.4587</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>42194.369</t>
+          <t>42194369015.7217</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>42455.417</t>
+          <t>42455417327.0363</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>42236.584</t>
+          <t>42236584401.0295</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>41220.09</t>
+          <t>41220089871.3641</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5114.592</t>
+          <t>5114592005.43904</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5050.397</t>
+          <t>5050397458.99384</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4945.373</t>
+          <t>4945373426.299</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5210.599</t>
+          <t>5210599326.69538</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5317.495</t>
+          <t>5317495219.36193</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5369.195</t>
+          <t>5369195369</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5488.763</t>
+          <t>5488762918</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5677.239</t>
+          <t>5677239118</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>5760.728</t>
+          <t>5760728069</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5936.407</t>
+          <t>5936406620</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5983.249</t>
+          <t>5983249244</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>6409.294</t>
+          <t>6409294101</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6479.312</t>
+          <t>6479312411</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>6512.389</t>
+          <t>6512388590</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>6172.579</t>
+          <t>6172579253</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6653.528</t>
+          <t>6653528427.29386</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6558.125</t>
+          <t>6558125225.49215</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6659.477</t>
+          <t>6659476570.14462</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6856.273</t>
+          <t>6856272880.13977</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7066.93</t>
+          <t>7066930465.10046</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6961.417</t>
+          <t>6961416731.94834</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7127.012</t>
+          <t>7127011526.85595</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>7176.956</t>
+          <t>7176955593.93508</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7159.213</t>
+          <t>7159213271.18566</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7123.6</t>
+          <t>7123600011.05471</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>7199.949</t>
+          <t>7199948537.14686</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>7275.75</t>
+          <t>7275750066.84333</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>7282.681</t>
+          <t>7282680540.18446</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>7217.871</t>
+          <t>7217871138.19669</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>6982.465</t>
+          <t>6982465348.42156</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>50845.365</t>
+          <t>50845365050.5126</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>53343.046</t>
+          <t>53343045521.3928</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>55663.7</t>
+          <t>55663699525.1387</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>55335.436</t>
+          <t>55335436329.601</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>63289.03</t>
+          <t>63289030283.2379</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>61997.762</t>
+          <t>61997761768.2972</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>64581.67</t>
+          <t>64581670110.7665</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>67000.017</t>
+          <t>67000017055.0654</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>65303.248</t>
+          <t>65303248481.6216</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>69112.816</t>
+          <t>69112815842.1906</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>60280.812</t>
+          <t>60280811937.4406</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>57540.415</t>
+          <t>57540414517.2555</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>57444.212</t>
+          <t>57444211606.8405</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>58630.515</t>
+          <t>58630514679.0361</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>60602.234</t>
+          <t>60602234191.8695</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>408729.533</t>
+          <t>408729532907.89</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>422740.685</t>
+          <t>422740684945.954</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>429173.719</t>
+          <t>429173719058.416</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>434229.587</t>
+          <t>434229587334.143</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>433336.133</t>
+          <t>433336132594.373</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>447690.05</t>
+          <t>447690050382.461</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>457931.785</t>
+          <t>457931785421.459</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>446355.698</t>
+          <t>446355698248.271</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>461695.026</t>
+          <t>461695025670.482</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>465360.993</t>
+          <t>465360993412.491</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>468780.92</t>
+          <t>468780919950.533</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>463833.094</t>
+          <t>463833093857.914</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>449591.928</t>
+          <t>449591927559.544</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>455869.88</t>
+          <t>455869880085.226</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>460912.884</t>
+          <t>460912884317.789</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1929.917</t>
+          <t>1929917147.60251</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2034.51</t>
+          <t>2034509849.31277</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2130.014</t>
+          <t>2130014101.6263</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2308.418</t>
+          <t>2308418033.48914</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2458.008</t>
+          <t>2458008026.38916</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2578.571</t>
+          <t>2578571039.99907</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2667.309</t>
+          <t>2667309175.65362</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2691.109</t>
+          <t>2691108649.85751</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2729.001</t>
+          <t>2729000750.27981</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2809.265</t>
+          <t>2809265001.64934</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2977.279</t>
+          <t>2977278513.48593</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3109.725</t>
+          <t>3109725073.94992</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>3164.381</t>
+          <t>3164381155.58501</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3056.794</t>
+          <t>3056793726.46356</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2739.318</t>
+          <t>2739317842.58637</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>26426.569</t>
+          <t>26426568700</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>26837.401</t>
+          <t>26837401000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>26858999500</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>27355.531</t>
+          <t>27355530800</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>27748.134</t>
+          <t>27748134200</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>28310.735</t>
+          <t>28310734600</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>28707.965</t>
+          <t>28707965400</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>29182.183</t>
+          <t>29182183200</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>29479.918</t>
+          <t>29479918000</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>29718.084</t>
+          <t>29718083900</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>30039.004</t>
+          <t>30039004500</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>30792.788</t>
+          <t>30792788300</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>31249.713</t>
+          <t>31249713300</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>31549.881</t>
+          <t>31549881000</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>30509.279</t>
+          <t>30509279400</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>102785.336</t>
+          <t>102785336309.266</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>103927.218</t>
+          <t>103927217679.788</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>103369.217</t>
+          <t>103369217150.21</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>101246.989</t>
+          <t>101246988677.691</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>99076.807</t>
+          <t>99076807477.4328</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>100177.904</t>
+          <t>100177904290.721</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>99460.607</t>
+          <t>99460607407.5732</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>97626.584</t>
+          <t>97626583840.2885</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>97944.352</t>
+          <t>97944352454.1957</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>98147.153</t>
+          <t>98147153379.7101</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>96831.355</t>
+          <t>96831355076.2254</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>99350.695</t>
+          <t>99350695264.1884</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>99761.612</t>
+          <t>99761612250.3796</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>97421.377</t>
+          <t>97421377310.7341</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>89716.478</t>
+          <t>89716477994.8995</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>32640.761</t>
+          <t>32640760630.5048</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>32366.566</t>
+          <t>32366566359.3398</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>32542.482</t>
+          <t>32542481626.3838</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>29972.52</t>
+          <t>29972519642.6025</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>31616.61</t>
+          <t>31616610207.0647</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>32772.416</t>
+          <t>32772416215.0786</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>33139.63</t>
+          <t>33139630374.6316</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>34146.109</t>
+          <t>34146108978.1279</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>34675.124</t>
+          <t>34675124347.6904</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>37056.547</t>
+          <t>37056547061.771</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>36350.538</t>
+          <t>36350537931.0334</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>36940.81</t>
+          <t>36940810197.7035</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>36652.904</t>
+          <t>36652903972.2718</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>36876.55</t>
+          <t>36876549870.3788</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>36765.509</t>
+          <t>36765508899.99</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2087.973</t>
+          <t>2087973000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1988.28</t>
+          <t>1988280000</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1990.438</t>
+          <t>1990438000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2076.019</t>
+          <t>2076018674.27178</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2016.758</t>
+          <t>2016758000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2079.554</t>
+          <t>2079554000</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1980.536</t>
+          <t>1980536270.47619</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2019.223</t>
+          <t>2019223254.9505</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2053.925</t>
+          <t>2053925000</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2112.124</t>
+          <t>2112123969.96663</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2274.689</t>
+          <t>2274689000</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2341.042</t>
+          <t>2341041784.49537</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2475.446</t>
+          <t>2475446000</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2553.702</t>
+          <t>2553701952.54095</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2306.659</t>
+          <t>2306658737.99467</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>314.909</t>
+          <t>314909260.115843</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>322.522</t>
+          <t>322522139.691882</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>334.262</t>
+          <t>334261571.025526</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>348.888</t>
+          <t>348888110.389039</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>370.292</t>
+          <t>370291801.692321</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>393.85</t>
+          <t>393849815.76532</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>414.011</t>
+          <t>414010620.901615</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>426.888</t>
+          <t>426888453.077314</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>435.429</t>
+          <t>435428796.830708</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>451.042</t>
+          <t>451041569.253607</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>465.533</t>
+          <t>465532524.894422</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>483.124</t>
+          <t>483123791.169618</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>505.824</t>
+          <t>505824273.094494</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>530.593</t>
+          <t>530592586.963389</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>535.24</t>
+          <t>535239727.255658</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1336.081</t>
+          <t>1336081307.41044</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1323.147</t>
+          <t>1323146895.9235</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1305.686</t>
+          <t>1305686489.00979</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1371.662</t>
+          <t>1371662037.92692</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1370.661</t>
+          <t>1370660915.40396</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1362.726</t>
+          <t>1362726259.10289</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1341.531</t>
+          <t>1341531498.4363</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1351.454</t>
+          <t>1351453782.44377</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1384.114</t>
+          <t>1384113728.95087</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1399.416</t>
+          <t>1399416320.30675</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1456.632</t>
+          <t>1456632329.86547</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1522.637</t>
+          <t>1522636753.83629</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1594.493</t>
+          <t>1594493377.14699</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1565.39</t>
+          <t>1565390254.85935</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1306.652</t>
+          <t>1306652451.44424</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>44931.874</t>
+          <t>44931874086.902</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>46891.213</t>
+          <t>46891212621.2412</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>49276.104</t>
+          <t>49276103823.411</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>50654.784</t>
+          <t>50654784208.5588</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>52599.157</t>
+          <t>52599156605.2384</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>54687.85</t>
+          <t>54687849781.3509</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>55434.331</t>
+          <t>55434331111.4983</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>56193.202</t>
+          <t>56193201728.5565</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>57784.359</t>
+          <t>57784358511.485</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>60451.696</t>
+          <t>60451696077.9388</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>61776.779</t>
+          <t>61776778710.5061</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>63475.481</t>
+          <t>63475481092.2066</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>64351.89</t>
+          <t>64351890264.3354</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>69062.343</t>
+          <t>69062343264.5907</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>67913.887</t>
+          <t>67913886561.8142</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>239.98</t>
+          <t>239979570.570101</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>241.04</t>
+          <t>241040263.441192</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>242.001</t>
+          <t>242001023.264924</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>245.359</t>
+          <t>245359299.619592</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>248.678</t>
+          <t>248678128.718725</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>251.485</t>
+          <t>251485020.101561</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>216.96</t>
+          <t>216960210.868469</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>256.499</t>
+          <t>256499350.402692</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>245.286</t>
+          <t>245286440.92271</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>250.577</t>
+          <t>250577276.888324</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>252.301</t>
+          <t>252301097.510267</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>253.898</t>
+          <t>253897875.799843</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>264.56</t>
+          <t>264559728.038222</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>271.437</t>
+          <t>271436883.391728</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>264.649</t>
+          <t>264648734.990132</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8502.439</t>
+          <t>8502438633.82475</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8679.178</t>
+          <t>8679178145.08419</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8931.979</t>
+          <t>8931978800.39168</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>9176.159</t>
+          <t>9176159249.43066</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>9443.354</t>
+          <t>9443353950.50529</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9648.194</t>
+          <t>9648194015.96294</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9833.376</t>
+          <t>9833376490</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>9812.115</t>
+          <t>9812114878</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>9726.175</t>
+          <t>9726174631</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>9580.306</t>
+          <t>9580306302</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>9554.199</t>
+          <t>9554198533</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>9704.286</t>
+          <t>9704286458</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>9945.624</t>
+          <t>9945624071</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>10062.514</t>
+          <t>10062514399</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>9905.508</t>
+          <t>9905507602</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15014.242</t>
+          <t>15014241815.3346</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15032.708</t>
+          <t>15032707867.3007</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15287.945</t>
+          <t>15287944968.716</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>15407.358</t>
+          <t>15407358482.0686</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15801.55</t>
+          <t>15801550161.6009</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>16365.614</t>
+          <t>16365614284.9565</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17542.312</t>
+          <t>17542311839.8331</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>16854.515</t>
+          <t>16854514610.4582</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>16906.382</t>
+          <t>16906382225.1846</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>17319.251</t>
+          <t>17319250893.9937</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>17709.691</t>
+          <t>17709690793.7366</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>18612.378</t>
+          <t>18612378276.4895</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>19705.785</t>
+          <t>19705785159.2337</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>20418.937</t>
+          <t>20418936958.2142</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>20070.824</t>
+          <t>20070824201.2121</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6769.189</t>
+          <t>6769189057.17861</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6753.915</t>
+          <t>6753915358.02492</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6802.734</t>
+          <t>6802734105.03599</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6949.965</t>
+          <t>6949964879.60813</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7170.217</t>
+          <t>7170217229.08824</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7306.097</t>
+          <t>7306096701.79946</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7399.159</t>
+          <t>7399158866.51142</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>7507.101</t>
+          <t>7507101468.83552</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>7368.323</t>
+          <t>7368322769.92465</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>7502.137</t>
+          <t>7502137396.7577</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>7523.578</t>
+          <t>7523578475.91159</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>7933.461</t>
+          <t>7933461390.82089</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>7984.655</t>
+          <t>7984655273.33706</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>7978.693</t>
+          <t>7978692834.63733</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>7814.953</t>
+          <t>7814952668.66301</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>11128.807</t>
+          <t>11128807489.9963</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>11394.243</t>
+          <t>11394243144.4763</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>10468.573</t>
+          <t>10468573057.614</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10026.345</t>
+          <t>10026345038.1371</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>11606.427</t>
+          <t>11606427000</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>11478.276</t>
+          <t>11478276000</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>11318.912</t>
+          <t>11318912000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11929.299</t>
+          <t>11929299000</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>11555.4</t>
+          <t>11555400000</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>12477.476</t>
+          <t>12477476000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>11991.971</t>
+          <t>11991971000</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>12430.286</t>
+          <t>12430286000</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>12497.741</t>
+          <t>12497741000</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>12629.99</t>
+          <t>12629990000</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>12762.814</t>
+          <t>12762813634.0076</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>120664.857</t>
+          <t>120664856778.547</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>119341.921</t>
+          <t>119341921117.83</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>118011.108</t>
+          <t>118011107599.581</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>113027.024</t>
+          <t>113027023673.612</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>113179.63</t>
+          <t>113179630388.439</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>113940.227</t>
+          <t>113940226544.234</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>114153.881</t>
+          <t>114153881417.255</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>113749.879</t>
+          <t>113749879436.617</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>112966.14</t>
+          <t>112966140149.546</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>114564.731</t>
+          <t>114564730880.348</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>116454.544</t>
+          <t>116454543903.835</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>117538.537</t>
+          <t>117538536852.503</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>119035.202</t>
+          <t>119035202129.533</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>111132.001</t>
+          <t>111132000708.532</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>108212.079</t>
+          <t>108212078898.61</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3551.322</t>
+          <t>3551322000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3557.791</t>
+          <t>3557791000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3511.601</t>
+          <t>3511601000</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3439.541</t>
+          <t>3439541000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3305.355</t>
+          <t>3305355000</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3225.975</t>
+          <t>3225975000</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3198.825</t>
+          <t>3198825000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3099.35</t>
+          <t>3099350000</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2995.506</t>
+          <t>2995506000</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2990.358</t>
+          <t>2990358000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>3077.563</t>
+          <t>3077563000</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>3106.024</t>
+          <t>3106024000</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>3213.605</t>
+          <t>3213605000</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3258.575</t>
+          <t>3258575000</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3049.539</t>
+          <t>3049539000</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1287.888</t>
+          <t>1287887658.44177</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1269.261</t>
+          <t>1269260505.82646</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1237.461</t>
+          <t>1237460870.20158</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1237.419</t>
+          <t>1237419425.58602</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1255.282</t>
+          <t>1255281960.24692</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1280.997</t>
+          <t>1280996781.98652</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1294.77</t>
+          <t>1294769820.60965</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1311.437</t>
+          <t>1311436755.34495</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1313.919</t>
+          <t>1313919474.72281</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1319.254</t>
+          <t>1319253617.09501</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1322.093</t>
+          <t>1322092727.88369</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1343.542</t>
+          <t>1343541682.80064</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1387.787</t>
+          <t>1387787215.2592</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1430.053</t>
+          <t>1430053445.43154</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1393.705</t>
+          <t>1393704986.53083</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>6234.64</t>
+          <t>6234639999.99358</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6244.23</t>
+          <t>6244229999.9936</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6174.71</t>
+          <t>6174710000</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>6277.92</t>
+          <t>6277920000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6444.15</t>
+          <t>6444150000.00593</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6539.08</t>
+          <t>6539080000</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6609.93</t>
+          <t>6609930000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6527.4</t>
+          <t>6527400000.00494</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>6446.22</t>
+          <t>6446220000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>6489.13</t>
+          <t>6489130000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>6490.82</t>
+          <t>6490820000</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6587.61</t>
+          <t>6587610000</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>6822.76</t>
+          <t>6822760000</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>6920.38</t>
+          <t>6920380000</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>6705.67</t>
+          <t>6705669998.77628</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>21136.968</t>
+          <t>21136968495.3787</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>21928.844</t>
+          <t>21928843884.9571</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>22158.416</t>
+          <t>22158415768.4229</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>21473.141</t>
+          <t>21473141139.3276</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>21239.635</t>
+          <t>21239635051.3431</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>22266.289</t>
+          <t>22266289161.2901</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>21661.432</t>
+          <t>21661431709.0623</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>22352.358</t>
+          <t>22352358238.851</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>22401.434</t>
+          <t>22401434330.8751</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>22654.767</t>
+          <t>22654766570.73</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>24154.349</t>
+          <t>24154349353.4859</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>24257.62</t>
+          <t>24257620048.3281</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>23949.859</t>
+          <t>23949858672.7149</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>24573.739</t>
+          <t>24573738602.1549</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>24016.797</t>
+          <t>24016797173.8145</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>15097.83</t>
+          <t>15097830216.4054</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>14946.957</t>
+          <t>14946956845.1698</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15293.409</t>
+          <t>15293409103.6755</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>15229.189</t>
+          <t>15229189326.1391</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>15348.731</t>
+          <t>15348730504.7165</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>15665.324</t>
+          <t>15665324405.3071</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>14693.148</t>
+          <t>14693147569.6039</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>14840.401</t>
+          <t>14840400700.7909</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>15160.842</t>
+          <t>15160841982.1177</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>15843.53</t>
+          <t>15843529969.6984</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16187.971</t>
+          <t>16187970505.3992</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>16526.11</t>
+          <t>16526110478.8122</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>16946.724</t>
+          <t>16946724328.8859</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>17266.618</t>
+          <t>17266618144.9646</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>16712.116</t>
+          <t>16712115566.2901</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>222377.918</t>
+          <t>222377917711.506</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>226311.857</t>
+          <t>226311857377.698</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>232419.816</t>
+          <t>232419815564.116</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>238264.033</t>
+          <t>238264032694.127</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>243345.874</t>
+          <t>243345873747.246</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>248180.096</t>
+          <t>248180095947.989</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>245372.044</t>
+          <t>245372044378.705</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>242440.736</t>
+          <t>242440735569.293</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>240823.365</t>
+          <t>240823364771.45</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>243449.993</t>
+          <t>243449993125.228</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>247601.002</t>
+          <t>247601001874.047</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>252739.809</t>
+          <t>252739809254.507</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>254926.998</t>
+          <t>254926997513.093</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>252853.572</t>
+          <t>252853572165.955</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>240900.197</t>
+          <t>240900196848.347</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>684490.338</t>
+          <t>684490338211.679</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>706246.059</t>
+          <t>706246058804.897</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>723082.616</t>
+          <t>723082616373.875</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>727150.964</t>
+          <t>727150963878.283</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>734138.16</t>
+          <t>734138160140.059</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>762635.984</t>
+          <t>762635983824.331</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>796388.724</t>
+          <t>796388724368.756</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>816293.521</t>
+          <t>816293521413.016</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>858497.817</t>
+          <t>858497817332.735</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>902286.807</t>
+          <t>902286806961.455</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>926704.183</t>
+          <t>926704183455.952</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>964398.177</t>
+          <t>964398176874.085</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>995418.423</t>
+          <t>995418422823.631</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1040011.962</t>
+          <t>1040011962123.2</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1060308.098</t>
+          <t>1060308098055.14</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2540163.195</t>
+          <t>2540163194653.01</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2598384.756</t>
+          <t>2598384755765.98</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2647332.327</t>
+          <t>2647332326955.5</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2665359.155</t>
+          <t>2665359154981.25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2706491.456</t>
+          <t>2706491456051.62</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2788332.154</t>
+          <t>2788332153999.34</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2876310.617</t>
+          <t>2876310616768.06</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2925557.023</t>
+          <t>2925557022779.32</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>3011822.532</t>
+          <t>3011822532126.05</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>3110191.477</t>
+          <t>3110191476674.07</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>3156833.451</t>
+          <t>3156833450686.65</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>3215874.427</t>
+          <t>3215874427204.57</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>3270922.466</t>
+          <t>3270922465937.15</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>3356370.108</t>
+          <t>3356370108232.97</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>3371243.035</t>
+          <t>3371243035286.7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>hours_worked.empe.s.hr</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
